--- a/prosp_draft_data.xlsx
+++ b/prosp_draft_data.xlsx
@@ -5,25 +5,24 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristina/Library/CloudStorage/Dropbox/Kristina/Drafts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristina/Documents/GitHub/phd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48524361-1780-1B46-B0D4-FB74B08C4340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358FAC01-BA95-B94F-9CA4-3A435E255B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32120" windowHeight="19120" activeTab="1" xr2:uid="{C3B414E7-4F74-B640-BD11-B6FEEAE78456}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32120" windowHeight="19120" xr2:uid="{C3B414E7-4F74-B640-BD11-B6FEEAE78456}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
-    <sheet name="drafting database" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="state_poverty_by_race" sheetId="1" r:id="rId4"/>
+    <sheet name="drafting database" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="state_poverty_by_race" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="267">
   <si>
     <t>state</t>
   </si>
@@ -335,9 +334,6 @@
   </si>
   <si>
     <t>ealing is automatic for most pardoned crimes, and pardon may be an alternative for individuals who cannot get their records sealed - § 16-90-1411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States with Arrest </t>
   </si>
   <si>
     <t>Expungement/Sealing</t>
@@ -1533,14 +1529,14 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1917,21 +1913,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550F2F11-1CCC-5240-9A2E-ADA3232DB3F9}">
-  <dimension ref="A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADAEDBD-EDC3-1E4E-8B42-686F75F138A0}">
   <dimension ref="A1:BZ73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1952,77 +1933,77 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+        <v>264</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
       <c r="M1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
+        <v>258</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
     </row>
     <row r="2" spans="1:78" ht="159" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="F2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>98</v>
@@ -2034,169 +2015,169 @@
         <v>100</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="BM2" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="BT2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="BQ2" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="BT2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="BU2" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="BV2" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="BW2" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BY2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ2" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="BZ2" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2204,7 +2185,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M3" s="1">
         <v>77</v>
@@ -2219,7 +2200,7 @@
         <v>103</v>
       </c>
       <c r="BM3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2230,16 +2211,16 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M4" s="1">
         <v>49</v>
       </c>
       <c r="BM4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2250,16 +2231,16 @@
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M5" s="1">
         <v>26</v>
       </c>
       <c r="BM5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2270,13 +2251,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M6" s="1">
         <v>98</v>
       </c>
       <c r="BM6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:78" ht="238" x14ac:dyDescent="0.2">
@@ -2287,47 +2268,47 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M7" s="1">
         <v>116</v>
       </c>
       <c r="BM7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BN7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="BO7" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="BO7" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="BP7" s="1"/>
       <c r="BQ7" s="1"/>
       <c r="BR7" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BS7" s="1"/>
       <c r="BT7" s="1"/>
       <c r="BU7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="BV7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="BW7" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="BV7" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="BW7" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="BX7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BY7" s="1">
         <v>2015</v>
       </c>
       <c r="BZ7" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:78" ht="323" x14ac:dyDescent="0.2">
@@ -2338,16 +2319,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M8" s="1">
         <v>36</v>
       </c>
       <c r="BM8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2358,36 +2339,36 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M9" s="1">
         <v>105</v>
       </c>
       <c r="BM9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>2.5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M10" s="1">
         <v>45</v>
       </c>
       <c r="BM10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:78" ht="17" x14ac:dyDescent="0.2">
@@ -2395,7 +2376,7 @@
         <v>44</v>
       </c>
       <c r="BM11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:78" ht="17" x14ac:dyDescent="0.2">
@@ -2406,7 +2387,7 @@
         <v>128</v>
       </c>
       <c r="BM12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:78" ht="372" x14ac:dyDescent="0.2">
@@ -2417,16 +2398,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="M13" s="1">
         <v>127</v>
       </c>
       <c r="BM13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:78" ht="153" x14ac:dyDescent="0.2">
@@ -2437,16 +2418,16 @@
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M14" s="1">
         <v>28</v>
       </c>
       <c r="BM14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:78" ht="409.6" x14ac:dyDescent="0.2">
@@ -2457,13 +2438,13 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M15">
         <v>19</v>
       </c>
       <c r="BM15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:78" ht="356" x14ac:dyDescent="0.2">
@@ -2474,13 +2455,13 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M16">
         <v>78</v>
       </c>
       <c r="BM16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:65" ht="289" x14ac:dyDescent="0.2">
@@ -2491,16 +2472,16 @@
         <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="M17">
         <v>19</v>
       </c>
       <c r="BM17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2511,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M18">
         <v>105</v>
       </c>
       <c r="BM18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:65" ht="272" x14ac:dyDescent="0.2">
@@ -2528,13 +2509,13 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
       <c r="BM19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:65" ht="68" x14ac:dyDescent="0.2">
@@ -2545,13 +2526,13 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M20" s="1">
         <v>94</v>
       </c>
       <c r="BM20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2562,16 +2543,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="M21" s="1">
         <v>116</v>
       </c>
       <c r="BM21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:65" ht="204" x14ac:dyDescent="0.2">
@@ -2582,13 +2563,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M22" s="1">
         <v>32</v>
       </c>
       <c r="BM22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:65" ht="170" x14ac:dyDescent="0.2">
@@ -2599,16 +2580,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="M23" s="1">
         <v>163</v>
       </c>
       <c r="BM23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:65" ht="136" x14ac:dyDescent="0.2">
@@ -2619,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M24" s="1">
         <v>102</v>
       </c>
       <c r="BM24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:65" ht="187" x14ac:dyDescent="0.2">
@@ -2636,16 +2617,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="M25" s="1">
         <v>79</v>
       </c>
       <c r="BM25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2656,16 +2637,16 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="M26" s="1">
         <v>171</v>
       </c>
       <c r="BM26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2676,13 +2657,13 @@
         <v>2.5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M27" s="1">
         <v>166</v>
       </c>
       <c r="BM27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2693,16 +2674,16 @@
         <v>3</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M28" s="1">
         <v>69</v>
       </c>
       <c r="BM28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2713,13 +2694,13 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M29" s="1">
         <v>100</v>
       </c>
       <c r="BM29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:65" ht="34" x14ac:dyDescent="0.2">
@@ -2730,13 +2711,13 @@
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M30" s="1">
         <v>42</v>
       </c>
       <c r="BM30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2747,13 +2728,13 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M31" s="1">
         <v>58</v>
       </c>
       <c r="BM31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
@@ -2764,13 +2745,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M32" s="1">
         <v>78</v>
       </c>
       <c r="BM32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -2781,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="M33" s="1">
         <v>114</v>
       </c>
       <c r="BM33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:67" ht="272" x14ac:dyDescent="0.2">
@@ -2801,16 +2782,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="M34" s="1">
         <v>44</v>
       </c>
       <c r="BM34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -2821,19 +2802,19 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="M35" s="1">
         <v>151</v>
       </c>
       <c r="BM35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BN35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BO35">
         <v>2005</v>
@@ -2847,13 +2828,13 @@
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M36" s="1">
         <v>109</v>
       </c>
       <c r="BM36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:67" ht="204" x14ac:dyDescent="0.2">
@@ -2864,13 +2845,13 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M37" s="1">
         <v>54</v>
       </c>
       <c r="BM37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -2878,13 +2859,13 @@
         <v>71</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M38" s="1">
         <v>74</v>
       </c>
       <c r="BM38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:67" ht="404" x14ac:dyDescent="0.2">
@@ -2895,16 +2876,16 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M39" s="1">
         <v>27</v>
       </c>
       <c r="BM39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:67" ht="289" x14ac:dyDescent="0.2">
@@ -2915,16 +2896,16 @@
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="M40" s="1">
         <v>37</v>
       </c>
       <c r="BM40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -2935,16 +2916,16 @@
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="M41" s="1">
         <v>106</v>
       </c>
       <c r="BM41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:67" ht="255" x14ac:dyDescent="0.2">
@@ -2955,19 +2936,19 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="M42" s="1">
         <v>104</v>
       </c>
       <c r="BM42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:67" ht="340" x14ac:dyDescent="0.2">
@@ -2975,16 +2956,16 @@
         <v>76</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M43" s="1">
         <v>153</v>
       </c>
       <c r="BM43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -2995,16 +2976,16 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="M44" s="1">
         <v>32</v>
       </c>
       <c r="BM44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:67" ht="17" x14ac:dyDescent="0.2">
@@ -3015,7 +2996,7 @@
         <v>115</v>
       </c>
       <c r="BM45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -3026,16 +3007,16 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="M46" s="1">
         <v>150</v>
       </c>
       <c r="BM46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:67" ht="409.6" x14ac:dyDescent="0.2">
@@ -3043,19 +3024,19 @@
         <v>80</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="M47" s="1">
         <v>29</v>
       </c>
       <c r="BM47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:67" ht="238" x14ac:dyDescent="0.2">
@@ -3066,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M48" s="1">
         <v>49</v>
       </c>
       <c r="BM48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:65" ht="34" x14ac:dyDescent="0.2">
@@ -3080,33 +3061,33 @@
         <v>82</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M49" s="1">
         <v>117</v>
       </c>
       <c r="BM49" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:65" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>2.5</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="M50" s="1">
         <v>109</v>
       </c>
       <c r="BM50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:65" ht="409.6" x14ac:dyDescent="0.25">
@@ -3114,19 +3095,19 @@
         <v>84</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I51" s="7" t="s">
         <v>193</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="M51" s="1">
         <v>111</v>
       </c>
       <c r="BM51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:65" ht="272" x14ac:dyDescent="0.2">
@@ -3134,13 +3115,13 @@
         <v>85</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M52" s="1">
         <v>118</v>
       </c>
       <c r="BM52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:65" ht="404" x14ac:dyDescent="0.2">
@@ -3151,25 +3132,25 @@
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="J53" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="M53" s="1">
         <v>15</v>
       </c>
       <c r="BM53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:65" ht="17" x14ac:dyDescent="0.2">
@@ -3245,7 +3226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07317766-2635-6C4C-99D4-940F0F196B90}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3254,7 +3235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40844099-4515-6649-9C1F-21095DA7B62A}">
   <dimension ref="A1:AI72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/prosp_draft_data.xlsx
+++ b/prosp_draft_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristina/Documents/GitHub/phd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358FAC01-BA95-B94F-9CA4-3A435E255B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D589B06-2792-AF4D-BDA3-AC4F64C6BBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32120" windowHeight="19120" xr2:uid="{C3B414E7-4F74-B640-BD11-B6FEEAE78456}"/>
+    <workbookView xWindow="-4680" yWindow="-20680" windowWidth="32120" windowHeight="19020" xr2:uid="{C3B414E7-4F74-B640-BD11-B6FEEAE78456}"/>
   </bookViews>
   <sheets>
     <sheet name="drafting database" sheetId="2" r:id="rId1"/>
@@ -2799,7 +2799,7 @@
         <v>68</v>
       </c>
       <c r="B35" s="2">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>218</v>
